--- a/results/04_final_refined_daily_hydroclimate_data/508/Dry_bulb_temp_15h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/508/Dry_bulb_temp_15h00_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
@@ -693,8 +693,8 @@
       <c r="C22">
         <v>21</v>
       </c>
-      <c r="D22">
-        <v>29.9</v>
+      <c r="D22" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -707,8 +707,8 @@
       <c r="C23">
         <v>22</v>
       </c>
-      <c r="D23">
-        <v>28.9</v>
+      <c r="D23" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -721,8 +721,8 @@
       <c r="C24">
         <v>23</v>
       </c>
-      <c r="D24">
-        <v>24.8</v>
+      <c r="D24" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -735,8 +735,8 @@
       <c r="C25">
         <v>24</v>
       </c>
-      <c r="D25">
-        <v>28</v>
+      <c r="D25" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -749,8 +749,8 @@
       <c r="C26">
         <v>25</v>
       </c>
-      <c r="D26">
-        <v>31.2</v>
+      <c r="D26" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:4">

--- a/results/04_final_refined_daily_hydroclimate_data/508/Dry_bulb_temp_15h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/508/Dry_bulb_temp_15h00_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
@@ -483,8 +483,8 @@
       <c r="C7">
         <v>6</v>
       </c>
-      <c r="D7" t="s">
-        <v>4</v>
+      <c r="D7">
+        <v>28.4</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -497,8 +497,8 @@
       <c r="C8">
         <v>7</v>
       </c>
-      <c r="D8" t="s">
-        <v>4</v>
+      <c r="D8">
+        <v>24.3</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -511,8 +511,8 @@
       <c r="C9">
         <v>8</v>
       </c>
-      <c r="D9" t="s">
-        <v>4</v>
+      <c r="D9">
+        <v>22.2</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -525,8 +525,8 @@
       <c r="C10">
         <v>9</v>
       </c>
-      <c r="D10" t="s">
-        <v>4</v>
+      <c r="D10">
+        <v>27.7</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -539,8 +539,8 @@
       <c r="C11">
         <v>10</v>
       </c>
-      <c r="D11" t="s">
-        <v>4</v>
+      <c r="D11">
+        <v>26.6</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -693,8 +693,8 @@
       <c r="C22">
         <v>21</v>
       </c>
-      <c r="D22" t="s">
-        <v>4</v>
+      <c r="D22">
+        <v>29.9</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -707,8 +707,8 @@
       <c r="C23">
         <v>22</v>
       </c>
-      <c r="D23" t="s">
-        <v>4</v>
+      <c r="D23">
+        <v>28.9</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -721,8 +721,8 @@
       <c r="C24">
         <v>23</v>
       </c>
-      <c r="D24" t="s">
-        <v>4</v>
+      <c r="D24">
+        <v>24.8</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -735,8 +735,8 @@
       <c r="C25">
         <v>24</v>
       </c>
-      <c r="D25" t="s">
-        <v>4</v>
+      <c r="D25">
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -749,8 +749,8 @@
       <c r="C26">
         <v>25</v>
       </c>
-      <c r="D26" t="s">
-        <v>4</v>
+      <c r="D26">
+        <v>31.2</v>
       </c>
     </row>
     <row r="27" spans="1:4">

--- a/results/04_final_refined_daily_hydroclimate_data/508/Dry_bulb_temp_15h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/508/Dry_bulb_temp_15h00_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
@@ -498,7 +498,7 @@
         <v>7</v>
       </c>
       <c r="D8">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -567,8 +567,8 @@
       <c r="C13">
         <v>12</v>
       </c>
-      <c r="D13" t="s">
-        <v>4</v>
+      <c r="D13">
+        <v>19.9</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -595,8 +595,8 @@
       <c r="C15">
         <v>14</v>
       </c>
-      <c r="D15" t="s">
-        <v>4</v>
+      <c r="D15">
+        <v>19.2</v>
       </c>
     </row>
     <row r="16" spans="1:4">

--- a/results/04_final_refined_daily_hydroclimate_data/508/Dry_bulb_temp_15h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/508/Dry_bulb_temp_15h00_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
@@ -498,7 +498,7 @@
         <v>7</v>
       </c>
       <c r="D8">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -567,8 +567,8 @@
       <c r="C13">
         <v>12</v>
       </c>
-      <c r="D13">
-        <v>19.9</v>
+      <c r="D13" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -595,8 +595,8 @@
       <c r="C15">
         <v>14</v>
       </c>
-      <c r="D15">
-        <v>19.2</v>
+      <c r="D15" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -763,8 +763,8 @@
       <c r="C27">
         <v>26</v>
       </c>
-      <c r="D27" t="s">
-        <v>4</v>
+      <c r="D27">
+        <v>26.4</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -777,8 +777,8 @@
       <c r="C28">
         <v>27</v>
       </c>
-      <c r="D28" t="s">
-        <v>4</v>
+      <c r="D28">
+        <v>31.2</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -791,8 +791,8 @@
       <c r="C29">
         <v>28</v>
       </c>
-      <c r="D29" t="s">
-        <v>4</v>
+      <c r="D29">
+        <v>24.1</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -805,8 +805,8 @@
       <c r="C30">
         <v>29</v>
       </c>
-      <c r="D30" t="s">
-        <v>4</v>
+      <c r="D30">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
